--- a/project1/reports/continue.dev/comparison prompt 2.xlsx
+++ b/project1/reports/continue.dev/comparison prompt 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\University\Project Bachelor\project 1 small\reports\continue.dev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\University\Project Bachelor\unit-testing-with-genai\project1\reports\continue.dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD169661-A30E-406A-A560-2C6031D84DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8B56B1-91F1-454C-8963-AED729060BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1035" windowWidth="29040" windowHeight="15720" xr2:uid="{5C34DE08-A12C-4EAA-A114-EBB56ADF1C7F}"/>
+    <workbookView xWindow="28680" yWindow="-1035" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="7" xr2:uid="{5C34DE08-A12C-4EAA-A114-EBB56ADF1C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="MyMath.checkSign(int)" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="102">
   <si>
     <t>testing a normal positive number</t>
   </si>
@@ -279,30 +279,6 @@
     <t>x is around  Integer.MAX_VALUE, y is large enough to cause overflow</t>
   </si>
   <si>
-    <t>general rule</t>
-  </si>
-  <si>
-    <t>Method names start with test</t>
-  </si>
-  <si>
-    <t>Boundary values checked</t>
-  </si>
-  <si>
-    <t>Private variables are used</t>
-  </si>
-  <si>
-    <t>Junit temporary storage is used</t>
-  </si>
-  <si>
-    <t>Edge cases tested</t>
-  </si>
-  <si>
-    <t>Methods have only a single assertion</t>
-  </si>
-  <si>
-    <t>Name of methods comply with what they test</t>
-  </si>
-  <si>
     <t>Qwen 3 Coder 30b</t>
   </si>
   <si>
@@ -349,6 +325,33 @@
   </si>
   <si>
     <t>test with multiple results (normal test)</t>
+  </si>
+  <si>
+    <t>قانون عمومی</t>
+  </si>
+  <si>
+    <t>متغیر های خصوصی استفاده شده است.</t>
+  </si>
+  <si>
+    <t>مقادیر مرزی مورد آزمون قرار گرفته اند.</t>
+  </si>
+  <si>
+    <t>روش JUnit برای حافظه موقت استفاده شده است.</t>
+  </si>
+  <si>
+    <t>موارد حاشیه ای تست شده اند.</t>
+  </si>
+  <si>
+    <t>آزمون ها ها فقط یک assertion دارند.</t>
+  </si>
+  <si>
+    <t>نام آزمون ها با test شروع می شود.</t>
+  </si>
+  <si>
+    <t>نام آزمون ها مشخص می کند که چه چیزی تست می شود.</t>
+  </si>
+  <si>
+    <t>در مخزن</t>
   </si>
 </sst>
 </file>
@@ -867,7 +870,7 @@
         <v>74</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1178,7 +1181,7 @@
         <v>74</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1496,7 +1499,7 @@
         <v>74</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1676,7 +1679,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
@@ -1711,7 +1714,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>24</v>
@@ -1781,13 +1784,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -1816,7 +1819,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>24</v>
@@ -1921,13 +1924,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>12</v>
@@ -1956,7 +1959,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>75</v>
@@ -1991,10 +1994,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C16" s="5">
         <v>0</v>
@@ -2026,13 +2029,13 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B17" s="5">
         <v>0</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>12</v>
@@ -2081,7 +2084,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
@@ -2105,7 +2108,7 @@
         <v>74</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -2472,7 +2475,7 @@
         <v>74</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -2695,7 +2698,7 @@
         <v>74</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -2729,7 +2732,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>11</v>
@@ -3237,7 +3240,7 @@
         <v>74</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -3271,7 +3274,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>11</v>
@@ -3512,22 +3515,22 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>69</v>
@@ -3548,12 +3551,12 @@
         <v>74</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>11</v>
@@ -3582,7 +3585,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>11</v>
@@ -3611,7 +3614,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>11</v>
@@ -3640,13 +3643,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>11</v>
@@ -3655,13 +3658,13 @@
         <v>12</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>11</v>
@@ -3669,7 +3672,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>12</v>
@@ -3698,28 +3701,28 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="F7" s="7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>11</v>
@@ -3727,7 +3730,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>11</v>
@@ -3745,7 +3748,7 @@
         <v>11</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>11</v>
